--- a/output/full_scan/batch_seq1_2026-06-26.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-26.xlsx
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>189.181372758515</v>
+        <v>189.1813727585149</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>5.29</v>
